--- a/data/zitate.xlsx
+++ b/data/zitate.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8938088B-A3DD-4039-A5CE-1CE9B45E6D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813E56D0-8BF5-4254-B5B1-7F51218EC8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="589">
   <si>
     <t>Author</t>
   </si>
@@ -1794,6 +1794,18 @@
   </si>
   <si>
     <t>Readers should not have to infer what was probably done; they should be told explicitly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Senn </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance is not a contribution to validity but to efficiency. </t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/feed/update/urn:li:ugcPost:7468996695083720704?commentUrn=urn%3Ali%3Acomment%3A%28ugcPost%3A7468996695083720704%2C7469211976741789696%29&amp;replyUrn=urn%3Ali%3Acomment%3A%28ugcPost%3A7468996695083720704%2C7469238588279304193%29&amp;dashCommentUrn=urn%3Ali%3Afsd_comment%3A%287469211976741789696%2Curn%3Ali%3AugcPost%3A7468996695083720704%29&amp;dashReplyUrn=urn%3Ali%3Afsd_comment%3A%287469238588279304193%2Curn%3Ali%3AugcPost%3A7468996695083720704%29</t>
+  </si>
+  <si>
+    <t>Causality</t>
   </si>
 </sst>
 </file>
@@ -1861,8 +1873,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2346,18 +2358,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H292"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H293"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.42578125" style="1" customWidth="1"/>
-    <col min="4" max="7" width="25.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="94.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="32.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.453125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="25.1796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="94.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2383,7 +2395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -2400,7 +2412,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2417,7 +2429,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -2437,7 +2449,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2451,7 +2463,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2462,7 +2474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2473,7 +2485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2487,7 +2499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -2501,7 +2513,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -2515,7 +2527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -2526,7 +2538,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -2537,7 +2549,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
@@ -2551,7 +2563,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -2565,7 +2577,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
@@ -2576,7 +2588,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="45.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="44.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>38</v>
       </c>
@@ -2590,7 +2602,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>42</v>
       </c>
@@ -2604,7 +2616,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>45</v>
       </c>
@@ -2615,7 +2627,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>47</v>
       </c>
@@ -2626,7 +2638,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>49</v>
       </c>
@@ -2640,7 +2652,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -2651,7 +2663,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -2662,7 +2674,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
@@ -2670,7 +2682,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>58</v>
       </c>
@@ -2678,7 +2690,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>59</v>
       </c>
@@ -2686,7 +2698,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,7 +2706,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>64</v>
       </c>
@@ -2702,7 +2714,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
@@ -2710,7 +2722,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>68</v>
       </c>
@@ -2718,7 +2730,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>70</v>
       </c>
@@ -2726,7 +2738,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>72</v>
       </c>
@@ -2734,7 +2746,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>74</v>
       </c>
@@ -2745,7 +2757,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>77</v>
       </c>
@@ -2753,7 +2765,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>79</v>
       </c>
@@ -2761,7 +2773,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>81</v>
       </c>
@@ -2769,7 +2781,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>83</v>
       </c>
@@ -2780,7 +2792,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>86</v>
       </c>
@@ -2791,7 +2803,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>89</v>
       </c>
@@ -2802,7 +2814,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>93</v>
       </c>
@@ -2810,7 +2822,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>95</v>
       </c>
@@ -2818,7 +2830,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>97</v>
       </c>
@@ -2829,7 +2841,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>14</v>
       </c>
@@ -2840,7 +2852,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>101</v>
       </c>
@@ -2851,7 +2863,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>104</v>
       </c>
@@ -2859,7 +2871,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>106</v>
       </c>
@@ -2867,7 +2879,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>108</v>
       </c>
@@ -2875,7 +2887,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>110</v>
       </c>
@@ -2883,7 +2895,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>112</v>
       </c>
@@ -2894,7 +2906,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>115</v>
       </c>
@@ -2902,7 +2914,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>117</v>
       </c>
@@ -2910,7 +2922,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>119</v>
       </c>
@@ -2918,7 +2930,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>121</v>
       </c>
@@ -2926,7 +2938,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>123</v>
       </c>
@@ -2934,7 +2946,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>125</v>
       </c>
@@ -2942,7 +2954,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>127</v>
       </c>
@@ -2953,7 +2965,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>129</v>
       </c>
@@ -2961,7 +2973,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>131</v>
       </c>
@@ -2969,7 +2981,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>131</v>
       </c>
@@ -2977,7 +2989,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>36</v>
       </c>
@@ -2988,7 +3000,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>136</v>
       </c>
@@ -2996,7 +3008,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>36</v>
       </c>
@@ -3004,7 +3016,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>140</v>
       </c>
@@ -3012,7 +3024,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>45</v>
       </c>
@@ -3020,7 +3032,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>143</v>
       </c>
@@ -3028,7 +3040,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C65" s="1" t="s">
         <v>144</v>
       </c>
@@ -3036,7 +3048,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>146</v>
       </c>
@@ -3044,7 +3056,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>148</v>
       </c>
@@ -3055,7 +3067,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>151</v>
       </c>
@@ -3066,7 +3078,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>154</v>
       </c>
@@ -3077,7 +3089,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>45</v>
       </c>
@@ -3088,7 +3100,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>160</v>
       </c>
@@ -3102,7 +3114,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>163</v>
       </c>
@@ -3113,7 +3125,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="29" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>167</v>
       </c>
@@ -3124,7 +3136,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>169</v>
       </c>
@@ -3132,7 +3144,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>171</v>
       </c>
@@ -3146,7 +3158,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>106</v>
       </c>
@@ -3160,7 +3172,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>177</v>
       </c>
@@ -3168,7 +3180,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>179</v>
       </c>
@@ -3176,7 +3188,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>183</v>
       </c>
@@ -3187,7 +3199,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>184</v>
       </c>
@@ -3198,7 +3210,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>10</v>
       </c>
@@ -3212,7 +3224,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>10</v>
       </c>
@@ -3223,7 +3235,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>190</v>
       </c>
@@ -3231,7 +3243,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>192</v>
       </c>
@@ -3245,7 +3257,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>196</v>
       </c>
@@ -3259,7 +3271,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>10</v>
       </c>
@@ -3273,7 +3285,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>10</v>
       </c>
@@ -3287,7 +3299,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>205</v>
       </c>
@@ -3298,7 +3310,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C89" s="1" t="s">
         <v>207</v>
       </c>
@@ -3306,12 +3318,12 @@
         <v>208</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C90" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>210</v>
       </c>
@@ -3319,7 +3331,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>212</v>
       </c>
@@ -3330,7 +3342,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>216</v>
       </c>
@@ -3341,7 +3353,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>219</v>
       </c>
@@ -3349,7 +3361,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>220</v>
       </c>
@@ -3360,7 +3372,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>223</v>
       </c>
@@ -3371,7 +3383,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>226</v>
       </c>
@@ -3379,7 +3391,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>229</v>
       </c>
@@ -3393,7 +3405,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>233</v>
       </c>
@@ -3407,7 +3419,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>163</v>
       </c>
@@ -3421,7 +3433,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>241</v>
       </c>
@@ -3435,7 +3447,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>241</v>
       </c>
@@ -3449,7 +3461,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="C103" s="1" t="s">
         <v>243</v>
       </c>
@@ -3457,7 +3469,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>246</v>
       </c>
@@ -3465,7 +3477,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>192</v>
       </c>
@@ -3476,7 +3488,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>249</v>
       </c>
@@ -3490,7 +3502,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>252</v>
       </c>
@@ -3498,7 +3510,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>254</v>
       </c>
@@ -3509,7 +3521,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>131</v>
       </c>
@@ -3523,7 +3535,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>257</v>
       </c>
@@ -3534,7 +3546,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>265</v>
       </c>
@@ -3545,7 +3557,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>254</v>
       </c>
@@ -3556,7 +3568,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>266</v>
       </c>
@@ -3567,7 +3579,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>271</v>
       </c>
@@ -3575,7 +3587,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>274</v>
       </c>
@@ -3586,7 +3598,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>277</v>
       </c>
@@ -3597,7 +3609,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>280</v>
       </c>
@@ -3608,7 +3620,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>280</v>
       </c>
@@ -3619,7 +3631,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>280</v>
       </c>
@@ -3630,7 +3642,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>285</v>
       </c>
@@ -3638,7 +3650,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>287</v>
       </c>
@@ -3649,7 +3661,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>290</v>
       </c>
@@ -3660,7 +3672,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>293</v>
       </c>
@@ -3671,7 +3683,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>293</v>
       </c>
@@ -3685,7 +3697,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>192</v>
       </c>
@@ -3696,7 +3708,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>300</v>
       </c>
@@ -3704,7 +3716,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>254</v>
       </c>
@@ -3712,7 +3724,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>303</v>
       </c>
@@ -3720,7 +3732,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>305</v>
       </c>
@@ -3728,7 +3740,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>307</v>
       </c>
@@ -3739,7 +3751,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>58</v>
       </c>
@@ -3747,7 +3759,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>49</v>
       </c>
@@ -3755,7 +3767,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>312</v>
       </c>
@@ -3763,7 +3775,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>314</v>
       </c>
@@ -3771,7 +3783,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>316</v>
       </c>
@@ -3782,7 +3794,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>319</v>
       </c>
@@ -3793,7 +3805,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>322</v>
       </c>
@@ -3801,7 +3813,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>325</v>
       </c>
@@ -3812,7 +3824,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>106</v>
       </c>
@@ -3823,7 +3835,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>329</v>
       </c>
@@ -3832,7 +3844,7 @@
       </c>
       <c r="H140"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>331</v>
       </c>
@@ -3843,7 +3855,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>254</v>
       </c>
@@ -3854,7 +3866,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>337</v>
       </c>
@@ -3865,7 +3877,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>339</v>
       </c>
@@ -3876,7 +3888,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>343</v>
       </c>
@@ -3884,7 +3896,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>58</v>
       </c>
@@ -3892,22 +3904,22 @@
         <v>344</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C147" s="1" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C148" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C149" s="1" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>349</v>
       </c>
@@ -3915,7 +3927,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>351</v>
       </c>
@@ -3923,7 +3935,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>353</v>
       </c>
@@ -3931,7 +3943,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>356</v>
       </c>
@@ -3942,7 +3954,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>360</v>
       </c>
@@ -3950,7 +3962,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>361</v>
       </c>
@@ -3958,7 +3970,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>363</v>
       </c>
@@ -3966,7 +3978,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>366</v>
       </c>
@@ -3974,47 +3986,47 @@
         <v>367</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C158" s="1" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="C159" s="1" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="C160" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C161" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C162" s="1" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C163" s="1" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C164" s="1" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C165" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>312</v>
       </c>
@@ -4022,32 +4034,32 @@
         <v>378</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C167" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C168" s="1" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C169" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C170" s="1" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C171" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C172" s="1" t="s">
         <v>386</v>
       </c>
@@ -4064,7 +4076,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>390</v>
       </c>
@@ -4072,7 +4084,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>392</v>
       </c>
@@ -4080,7 +4092,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>394</v>
       </c>
@@ -4088,7 +4100,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C176" s="1" t="s">
         <v>528</v>
       </c>
@@ -4102,22 +4114,22 @@
         <v>420</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C177" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C178" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C179" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>571</v>
       </c>
@@ -4131,7 +4143,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>400</v>
       </c>
@@ -4139,7 +4151,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C182" s="1" t="s">
         <v>414</v>
       </c>
@@ -4153,7 +4165,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>402</v>
       </c>
@@ -4170,7 +4182,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>409</v>
       </c>
@@ -4187,7 +4199,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C185" s="1" t="s">
         <v>410</v>
       </c>
@@ -4201,7 +4213,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C186" s="1" t="s">
         <v>411</v>
       </c>
@@ -4215,7 +4227,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C187" s="1" t="s">
         <v>412</v>
       </c>
@@ -4226,7 +4238,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C188" s="1" t="s">
         <v>373</v>
       </c>
@@ -4240,7 +4252,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C189" s="1" t="s">
         <v>416</v>
       </c>
@@ -4254,7 +4266,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C190" s="1" t="s">
         <v>418</v>
       </c>
@@ -4268,7 +4280,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C191" s="1" t="s">
         <v>421</v>
       </c>
@@ -4282,7 +4294,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C192" s="1" t="s">
         <v>424</v>
       </c>
@@ -4293,7 +4305,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C193" s="1" t="s">
         <v>425</v>
       </c>
@@ -4307,7 +4319,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>429</v>
       </c>
@@ -4324,7 +4336,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>430</v>
       </c>
@@ -4344,7 +4356,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C196" s="1" t="s">
         <v>433</v>
       </c>
@@ -4361,7 +4373,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C197" s="1" t="s">
         <v>435</v>
       </c>
@@ -4375,7 +4387,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C198" s="1" t="s">
         <v>437</v>
       </c>
@@ -4386,7 +4398,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C199" s="1" t="s">
         <v>438</v>
       </c>
@@ -4403,7 +4415,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>451</v>
       </c>
@@ -4423,7 +4435,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C201" s="1" t="s">
         <v>443</v>
       </c>
@@ -4437,7 +4449,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C202" s="1" t="s">
         <v>444</v>
       </c>
@@ -4451,7 +4463,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C203" s="1" t="s">
         <v>445</v>
       </c>
@@ -4465,7 +4477,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C204" s="1" t="s">
         <v>448</v>
       </c>
@@ -4479,7 +4491,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C205" s="1" t="s">
         <v>450</v>
       </c>
@@ -4493,7 +4505,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>451</v>
       </c>
@@ -4513,7 +4525,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C207" s="1" t="s">
         <v>365</v>
       </c>
@@ -4524,7 +4536,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C208" s="1" t="s">
         <v>372</v>
       </c>
@@ -4538,7 +4550,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C209" s="1" t="s">
         <v>454</v>
       </c>
@@ -4549,7 +4561,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C210" s="1" t="s">
         <v>383</v>
       </c>
@@ -4560,7 +4572,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C211" s="1" t="s">
         <v>384</v>
       </c>
@@ -4571,7 +4583,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C212" s="1" t="s">
         <v>455</v>
       </c>
@@ -4582,7 +4594,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>229</v>
       </c>
@@ -4599,7 +4611,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C214" s="1" t="s">
         <v>458</v>
       </c>
@@ -4613,7 +4625,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C215" s="1" t="s">
         <v>460</v>
       </c>
@@ -4630,7 +4642,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C216" s="1" t="s">
         <v>461</v>
       </c>
@@ -4647,7 +4659,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C217" s="1" t="s">
         <v>462</v>
       </c>
@@ -4658,7 +4670,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C218" s="1" t="s">
         <v>387</v>
       </c>
@@ -4675,7 +4687,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C219" s="1" t="s">
         <v>463</v>
       </c>
@@ -4692,7 +4704,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C220" s="1" t="s">
         <v>464</v>
       </c>
@@ -4706,7 +4718,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>466</v>
       </c>
@@ -4723,7 +4735,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="C222" s="1" t="s">
         <v>467</v>
       </c>
@@ -4737,7 +4749,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C223" s="1" t="s">
         <v>468</v>
       </c>
@@ -4751,7 +4763,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="C224" s="1" t="s">
         <v>469</v>
       </c>
@@ -4762,7 +4774,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="225" spans="3:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:6" ht="58" x14ac:dyDescent="0.35">
       <c r="C225" s="1" t="s">
         <v>472</v>
       </c>
@@ -4773,7 +4785,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="226" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C226" s="1" t="s">
         <v>473</v>
       </c>
@@ -4784,7 +4796,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="227" spans="3:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C227" s="1" t="s">
         <v>474</v>
       </c>
@@ -4798,7 +4810,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="228" spans="3:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C228" s="1" t="s">
         <v>476</v>
       </c>
@@ -4809,7 +4821,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="229" spans="3:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C229" s="1" t="s">
         <v>478</v>
       </c>
@@ -4820,7 +4832,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="230" spans="3:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C230" s="1" t="s">
         <v>479</v>
       </c>
@@ -4834,7 +4846,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="231" spans="3:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C231" s="1" t="s">
         <v>481</v>
       </c>
@@ -4845,7 +4857,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="232" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C232" s="1" t="s">
         <v>482</v>
       </c>
@@ -4856,7 +4868,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="233" spans="3:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C233" s="1" t="s">
         <v>483</v>
       </c>
@@ -4867,7 +4879,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="234" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C234" s="1" t="s">
         <v>484</v>
       </c>
@@ -4878,7 +4890,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="235" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C235" s="1" t="s">
         <v>485</v>
       </c>
@@ -4892,7 +4904,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="236" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C236" s="1" t="s">
         <v>368</v>
       </c>
@@ -4903,7 +4915,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="237" spans="3:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C237" s="1" t="s">
         <v>370</v>
       </c>
@@ -4914,7 +4926,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="238" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C238" s="1" t="s">
         <v>486</v>
       </c>
@@ -4925,7 +4937,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="239" spans="3:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:6" ht="29" x14ac:dyDescent="0.35">
       <c r="C239" s="1" t="s">
         <v>377</v>
       </c>
@@ -4936,7 +4948,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="240" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C240" s="1" t="s">
         <v>380</v>
       </c>
@@ -4950,7 +4962,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>388</v>
       </c>
@@ -4964,7 +4976,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C242" s="1" t="s">
         <v>487</v>
       </c>
@@ -4978,7 +4990,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C243" s="1" t="s">
         <v>488</v>
       </c>
@@ -4992,7 +5004,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C244" s="1" t="s">
         <v>489</v>
       </c>
@@ -5006,7 +5018,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>492</v>
       </c>
@@ -5026,7 +5038,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C246" s="1" t="s">
         <v>493</v>
       </c>
@@ -5043,7 +5055,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C247" s="1" t="s">
         <v>494</v>
       </c>
@@ -5060,7 +5072,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C248" s="1" t="s">
         <v>495</v>
       </c>
@@ -5077,7 +5089,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C249" s="1" t="s">
         <v>497</v>
       </c>
@@ -5088,7 +5100,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C250" s="1" t="s">
         <v>498</v>
       </c>
@@ -5102,7 +5114,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C251" s="1" t="s">
         <v>502</v>
       </c>
@@ -5113,7 +5125,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C252" s="1" t="s">
         <v>503</v>
       </c>
@@ -5127,7 +5139,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C253" s="1" t="s">
         <v>505</v>
       </c>
@@ -5138,7 +5150,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="C254" s="1" t="s">
         <v>506</v>
       </c>
@@ -5149,7 +5161,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C255" s="1" t="s">
         <v>507</v>
       </c>
@@ -5163,7 +5175,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>402</v>
       </c>
@@ -5177,7 +5189,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="C257" s="1" t="s">
         <v>509</v>
       </c>
@@ -5188,7 +5200,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C258" s="1" t="s">
         <v>510</v>
       </c>
@@ -5199,7 +5211,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>511</v>
       </c>
@@ -5213,7 +5225,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>513</v>
       </c>
@@ -5227,7 +5239,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="C261" s="1" t="s">
         <v>515</v>
       </c>
@@ -5241,7 +5253,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="C262" s="1" t="s">
         <v>516</v>
       </c>
@@ -5252,7 +5264,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>518</v>
       </c>
@@ -5269,7 +5281,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>519</v>
       </c>
@@ -5283,7 +5295,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>523</v>
       </c>
@@ -5297,7 +5309,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>525</v>
       </c>
@@ -5311,7 +5323,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>531</v>
       </c>
@@ -5325,7 +5337,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="268" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>533</v>
       </c>
@@ -5345,7 +5357,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>533</v>
       </c>
@@ -5359,7 +5371,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>533</v>
       </c>
@@ -5373,7 +5385,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>533</v>
       </c>
@@ -5387,7 +5399,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>540</v>
       </c>
@@ -5404,7 +5416,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>542</v>
       </c>
@@ -5415,7 +5427,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>545</v>
       </c>
@@ -5429,7 +5441,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>254</v>
       </c>
@@ -5443,7 +5455,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>550</v>
       </c>
@@ -5454,7 +5466,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>552</v>
       </c>
@@ -5462,7 +5474,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>553</v>
       </c>
@@ -5470,7 +5482,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>560</v>
       </c>
@@ -5481,7 +5493,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>555</v>
       </c>
@@ -5492,7 +5504,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>559</v>
       </c>
@@ -5500,7 +5512,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>562</v>
       </c>
@@ -5511,7 +5523,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>565</v>
       </c>
@@ -5519,7 +5531,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>565</v>
       </c>
@@ -5527,7 +5539,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>567</v>
       </c>
@@ -5538,7 +5550,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>570</v>
       </c>
@@ -5546,7 +5558,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>573</v>
       </c>
@@ -5557,7 +5569,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>576</v>
       </c>
@@ -5571,7 +5583,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>577</v>
       </c>
@@ -5585,7 +5597,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>565</v>
       </c>
@@ -5599,7 +5611,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>581</v>
       </c>
@@ -5613,7 +5625,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>583</v>
       </c>
@@ -5622,6 +5634,23 @@
       </c>
       <c r="D292" s="1" t="s">
         <v>500</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A293" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="H293" s="1" t="s">
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -5649,7 +5678,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/data/zitate.xlsx
+++ b/data/zitate.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813E56D0-8BF5-4254-B5B1-7F51218EC8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12113A9F-A55D-4CE7-95DC-9FCBAAD6BCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="70" windowWidth="35420" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="592">
   <si>
     <t>Author</t>
   </si>
@@ -1806,6 +1806,15 @@
   </si>
   <si>
     <t>Causality</t>
+  </si>
+  <si>
+    <t>Savielly Tartakower</t>
+  </si>
+  <si>
+    <t>Tactics is knowing what to do when there is something to do. Strategy is knowing what to do when there is nothing to do.</t>
+  </si>
+  <si>
+    <t>Strategy</t>
   </si>
 </sst>
 </file>
@@ -2358,7 +2367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:H294"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.453125" style="1" bestFit="1" customWidth="1"/>
@@ -5651,6 +5660,17 @@
       </c>
       <c r="H293" s="1" t="s">
         <v>587</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A294" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>591</v>
       </c>
     </row>
   </sheetData>

--- a/data/zitate.xlsx
+++ b/data/zitate.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12113A9F-A55D-4CE7-95DC-9FCBAAD6BCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4980F9CD-DE05-4A04-A76F-BAB5FBF8375F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="70" windowWidth="35420" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="594">
   <si>
     <t>Author</t>
   </si>
@@ -1815,6 +1815,12 @@
   </si>
   <si>
     <t>Strategy</t>
+  </si>
+  <si>
+    <t>Arthur Schopenhauer</t>
+  </si>
+  <si>
+    <t>Talent hits a target no one else can hit. Genius hits a target no one else can see.</t>
   </si>
 </sst>
 </file>
@@ -2367,7 +2373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H294"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.453125" style="1" bestFit="1" customWidth="1"/>
@@ -5671,6 +5677,17 @@
       </c>
       <c r="D294" s="1" t="s">
         <v>591</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A295" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>407</v>
       </c>
     </row>
   </sheetData>
